--- a/분석_인덱스.xlsx
+++ b/분석_인덱스.xlsx
@@ -1329,7 +1329,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>188건 전부 수집·검토. 분류 45건, 상태 21건, 금액 8건이 원자료와 다름. 그룹이 산 거래의 57%에서 인수 후 손상</t>
+          <t>188건 전부 수집·검토. 분류 45건, 상태 21건, 금액 10건이 원자료와 다름. 그룹이 산 거래 중 손상 여부를 판정할 수 있는 115건의 70%에서 인수 후 손상</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>impairment</t>
+          <t>impairment_class (2026-11-01 재분류)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>그룹이 산 139건 중 79건(57%) 손상, 53건 확인 안 됨. 로엔 1조 2,213억, Tapas·Radish 약 8,919억 전액 손상</t>
+          <t>그룹이 산 139건 중 판정 가능 115건(있음 81·없음 34)의 70% 손상. Kakao 81%, Naver 67%, CJ ENM 46%. 로엔 1조 2,213억, Tapas·Radish 약 8,919억 전액 손상</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>잠정 (확인 안 됨 53건, 생존 편향)</t>
+          <t>잠정 (식별 불가·미확인 15건 제외, 생존 편향)</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">

--- a/분석_인덱스.xlsx
+++ b/분석_인덱스.xlsx
@@ -1500,7 +1500,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Announced 21건 모두 실제 완료. 금액 불일치 8건(단위 오류 다수). 편입 전 28→44건</t>
+          <t>Announced 21건 모두 실제 완료. 금액 불일치 10건(단위 오류 다수). 편입 전 28→44건</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">

--- a/분석_인덱스.xlsx
+++ b/분석_인덱스.xlsx
@@ -1423,17 +1423,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>원자료 분류의 재판정</t>
+          <t>거래 형태 분류의 재판정</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>subtype_chk</t>
+          <t>subtype_chk (공시 확인)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>subtype(원자료 기반)</t>
+          <t>subtype (10-19 설명란 판정)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">

--- a/분석_인덱스.xlsx
+++ b/분석_인덱스.xlsx
@@ -1329,7 +1329,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>188건 전부 수집·검토. 분류 45건, 상태 21건, 금액 10건이 원자료와 다름. 그룹이 산 거래 중 손상 여부를 판정할 수 있는 115건의 70%에서 인수 후 손상</t>
+          <t>188건 전부 수집·검토. 거래 형태는 원자료에 없어 공시로 판정했고, 10-19 규칙과 값이 다른 45건을 전수 검수함(44건은 수집 판정이 맞음). 상태 21건, 금액 10건이 원자료와 다름. 그룹이 산 거래 중 손상 여부를 판정할 수 있는 114건의 71%에서 인수 후 손상</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1423,32 +1423,32 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>거래 형태 분류의 재판정</t>
+          <t>거래 형태 판정과 전수 검수</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>subtype_chk (공시 확인)</t>
+          <t>verdict·cause (검수 판정과 차이의 원인)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>subtype (10-19 설명란 판정)</t>
+          <t>subtype_chk (공시 확인) vs subtype (10-19 규칙)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>교차표</t>
+          <t>공시 원문 대조 (45건 전수)</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>45건 분류 변경. MA⑦ 16건은 모두 매수자 확인(매각 7, 외부자 4 등). 소수지분으로 보이던 단계적 인수 11건</t>
+          <t>10-19 규칙과 다른 45건 중 44건은 수집 판정이 맞음. 1건(IQTR594672156)은 MA③→MA⑥으로 고침. 원인: 정보 보충 22, 10-19 규칙 오판 16, 원자료 오류 4, 정의 차이 2, 수집 판정 오류 1. 최종 MA⑦ 0건</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>확인됨 (N009 결정 대기)</t>
+          <t>확인됨 (Brainer IQTR37372758·합작 펀드 계보 결정 대기)</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>meeting/20261102/주차연구정리_20261102.md [분석 B-2]</t>
+          <t>meeting/20261102/주차연구정리_20261102.md [분석 B-2] / nbs/ma188_subtype_audit.py, data/ma188_subtype_audit.csv</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>그룹이 산 139건 중 판정 가능 115건(있음 81·없음 34)의 70% 손상. Kakao 81%, Naver 67%, CJ ENM 46%. 로엔 1조 2,213억, Tapas·Radish 약 8,919억 전액 손상</t>
+          <t>그룹이 산 138건 중 판정 가능 114건(있음 81·없음 33)의 71% 손상. Kakao 81%, Naver 68%, CJ ENM 46%. 로엔 1조 2,213억, Tapas·Radish 약 8,919억 전액 손상</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
